--- a/data_lake/datos_diarios_preliminares/dt=2026-07-29/Temp-max-julio-26.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-07-29/Temp-max-julio-26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.187.8\Oficina\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0130718-98BB-445C-8536-09BA215828CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD3FF44-849A-4A2C-919C-21A7A0FB872A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TMAX_PRINCIPALES_CIUDADES" sheetId="1" r:id="rId1"/>
@@ -1219,7 +1219,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1435,6 +1435,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -9505,13 +9511,15 @@
       <c r="AE5" s="57">
         <v>31.3</v>
       </c>
-      <c r="AF5" s="57"/>
+      <c r="AF5" s="57">
+        <v>30.1</v>
+      </c>
       <c r="AG5" s="57"/>
       <c r="AH5" s="57"/>
       <c r="AI5" s="57"/>
       <c r="AJ5" s="37">
         <f>+IF(SUM($E5:$AI5)&gt;0,LOOKUP(1000,$E5:$AI5),NA())</f>
-        <v>31.3</v>
+        <v>30.1</v>
       </c>
       <c r="AK5" s="21">
         <f>+MAX($E5:$AI5)</f>
@@ -9529,11 +9537,11 @@
       </c>
       <c r="AO5" s="23">
         <f>IF(COUNTIF(E5:AI5,"&gt;0")&gt;=15,AVERAGE(E5:AI5),"")</f>
-        <v>31.07407407407408</v>
+        <v>31.039285714285718</v>
       </c>
       <c r="AP5" s="23">
         <f>IF(AN5&gt;0,IFERROR(AO5-AN5,""),"")</f>
-        <v>0.87670229806585098</v>
+        <v>0.84191393827748939</v>
       </c>
     </row>
     <row r="6" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9630,13 +9638,15 @@
       <c r="AE6" s="57">
         <v>31</v>
       </c>
-      <c r="AF6" s="57"/>
+      <c r="AF6" s="57">
+        <v>29.5</v>
+      </c>
       <c r="AG6" s="57"/>
       <c r="AH6" s="57"/>
       <c r="AI6" s="57"/>
       <c r="AJ6" s="37">
         <f t="shared" ref="AJ6:AJ48" si="0">+IF(SUM($E6:$AI6)&gt;0,LOOKUP(1000,$E6:$AI6),NA())</f>
-        <v>31</v>
+        <v>29.5</v>
       </c>
       <c r="AK6" s="21">
         <f t="shared" ref="AK6:AK48" si="1">+MAX($E6:$AI6)</f>
@@ -9654,11 +9664,11 @@
       </c>
       <c r="AO6" s="23">
         <f t="shared" ref="AO6:AO15" si="3">IF(COUNTIF(E6:AI6,"&gt;0")&gt;=15,AVERAGE(E6:AI6),"")</f>
-        <v>30.637037037037036</v>
+        <v>30.596428571428568</v>
       </c>
       <c r="AP6" s="23">
         <f t="shared" ref="AP6:AP48" si="4">IF(AN6&gt;0,IFERROR(AO6-AN6,""),"")</f>
-        <v>-1.7243359985304352E-2</v>
+        <v>-5.7851825593772332E-2</v>
       </c>
     </row>
     <row r="7" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9755,7 +9765,9 @@
       <c r="AE7" s="57">
         <v>34.4</v>
       </c>
-      <c r="AF7" s="57"/>
+      <c r="AF7" s="57">
+        <v>34.4</v>
+      </c>
       <c r="AG7" s="57"/>
       <c r="AH7" s="57"/>
       <c r="AI7" s="57"/>
@@ -9779,11 +9791,11 @@
       </c>
       <c r="AO7" s="23">
         <f t="shared" si="3"/>
-        <v>35.396296296296299</v>
+        <v>35.360714285714288</v>
       </c>
       <c r="AP7" s="23">
         <f t="shared" si="4"/>
-        <v>2.0302802887272264</v>
+        <v>1.9946982781452149</v>
       </c>
     </row>
     <row r="8" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9880,13 +9892,15 @@
       <c r="AE8" s="57">
         <v>32.6</v>
       </c>
-      <c r="AF8" s="57"/>
+      <c r="AF8" s="57">
+        <v>33.4</v>
+      </c>
       <c r="AG8" s="57"/>
       <c r="AH8" s="57"/>
       <c r="AI8" s="57"/>
       <c r="AJ8" s="37">
         <f t="shared" si="0"/>
-        <v>32.6</v>
+        <v>33.4</v>
       </c>
       <c r="AK8" s="21">
         <f t="shared" si="1"/>
@@ -9904,11 +9918,11 @@
       </c>
       <c r="AO8" s="23">
         <f t="shared" si="3"/>
-        <v>33.144444444444446</v>
+        <v>33.153571428571432</v>
       </c>
       <c r="AP8" s="23">
         <f t="shared" si="4"/>
-        <v>0.8954014336917524</v>
+        <v>0.90452841781873872</v>
       </c>
     </row>
     <row r="9" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10005,35 +10019,37 @@
       <c r="AE9" s="57">
         <v>32.9</v>
       </c>
-      <c r="AF9" s="57"/>
+      <c r="AF9" s="57">
+        <v>37.299999999999997</v>
+      </c>
       <c r="AG9" s="57"/>
       <c r="AH9" s="57"/>
       <c r="AI9" s="57"/>
       <c r="AJ9" s="37">
         <f t="shared" si="0"/>
-        <v>32.9</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="AK9" s="21">
         <f t="shared" si="1"/>
-        <v>35.799999999999997</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="AL9" s="22">
         <v>38.4</v>
       </c>
       <c r="AM9" s="23">
         <f t="shared" si="2"/>
-        <v>-2.6000000000000014</v>
+        <v>-1.1000000000000014</v>
       </c>
       <c r="AN9" s="23">
         <v>33.091246137683846</v>
       </c>
       <c r="AO9" s="23">
         <f t="shared" si="3"/>
-        <v>33.785185185185185</v>
+        <v>33.910714285714285</v>
       </c>
       <c r="AP9" s="23">
         <f t="shared" si="4"/>
-        <v>0.69393904750133828</v>
+        <v>0.81946814803043821</v>
       </c>
     </row>
     <row r="10" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10130,35 +10146,37 @@
       <c r="AE10" s="57">
         <v>35.1</v>
       </c>
-      <c r="AF10" s="57"/>
+      <c r="AF10" s="57">
+        <v>37.299999999999997</v>
+      </c>
       <c r="AG10" s="57"/>
       <c r="AH10" s="57"/>
       <c r="AI10" s="57"/>
       <c r="AJ10" s="37">
         <f t="shared" si="0"/>
-        <v>35.1</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="AK10" s="21">
         <f t="shared" si="1"/>
-        <v>37.1</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="AL10" s="22">
         <v>39.200000000000003</v>
       </c>
       <c r="AM10" s="23">
         <f t="shared" si="2"/>
-        <v>-2.1000000000000014</v>
+        <v>-1.9000000000000057</v>
       </c>
       <c r="AN10" s="23">
         <v>35.380238227660357</v>
       </c>
       <c r="AO10" s="23">
         <f t="shared" si="3"/>
-        <v>35.833333333333329</v>
+        <v>35.885714285714279</v>
       </c>
       <c r="AP10" s="23">
         <f t="shared" si="4"/>
-        <v>0.45309510567297195</v>
+        <v>0.50547605805392237</v>
       </c>
     </row>
     <row r="11" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10255,35 +10273,37 @@
       <c r="AE11" s="57">
         <v>37.6</v>
       </c>
-      <c r="AF11" s="57"/>
+      <c r="AF11" s="81">
+        <v>40.799999999999997</v>
+      </c>
       <c r="AG11" s="57"/>
       <c r="AH11" s="57"/>
       <c r="AI11" s="57"/>
       <c r="AJ11" s="37">
         <f t="shared" si="0"/>
-        <v>37.6</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="AK11" s="21">
         <f t="shared" si="1"/>
-        <v>40.5</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="AL11" s="22">
         <v>41.4</v>
       </c>
       <c r="AM11" s="23">
         <f t="shared" si="2"/>
-        <v>-0.89999999999999858</v>
+        <v>-0.60000000000000142</v>
       </c>
       <c r="AN11" s="23">
         <v>35.537284092848601</v>
       </c>
       <c r="AO11" s="23">
         <f t="shared" si="3"/>
-        <v>38.037037037037031</v>
+        <v>38.135714285714279</v>
       </c>
       <c r="AP11" s="23">
         <f t="shared" si="4"/>
-        <v>2.4997529441884296</v>
+        <v>2.5984301928656777</v>
       </c>
     </row>
     <row r="12" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10380,13 +10400,15 @@
       <c r="AE12" s="57">
         <v>33.200000000000003</v>
       </c>
-      <c r="AF12" s="57"/>
+      <c r="AF12" s="57">
+        <v>34.6</v>
+      </c>
       <c r="AG12" s="57"/>
       <c r="AH12" s="57"/>
       <c r="AI12" s="57"/>
       <c r="AJ12" s="37">
         <f t="shared" si="0"/>
-        <v>33.200000000000003</v>
+        <v>34.6</v>
       </c>
       <c r="AK12" s="21">
         <f t="shared" si="1"/>
@@ -10404,11 +10426,11 @@
       </c>
       <c r="AO12" s="23">
         <f t="shared" si="3"/>
-        <v>34.629629629629626</v>
+        <v>34.628571428571426</v>
       </c>
       <c r="AP12" s="23">
         <f t="shared" si="4"/>
-        <v>2.4410054834558892</v>
+        <v>2.4399472823976893</v>
       </c>
     </row>
     <row r="13" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10505,13 +10527,15 @@
       <c r="AE13" s="57">
         <v>33</v>
       </c>
-      <c r="AF13" s="57"/>
+      <c r="AF13" s="57">
+        <v>34.799999999999997</v>
+      </c>
       <c r="AG13" s="57"/>
       <c r="AH13" s="57"/>
       <c r="AI13" s="57"/>
       <c r="AJ13" s="37">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="AK13" s="21">
         <f t="shared" si="1"/>
@@ -10529,11 +10553,11 @@
       </c>
       <c r="AO13" s="23">
         <f t="shared" si="3"/>
-        <v>35.318518518518516</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="AP13" s="23">
         <f t="shared" si="4"/>
-        <v>1.9367264038231795</v>
+        <v>1.9182078853046605</v>
       </c>
     </row>
     <row r="14" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10630,13 +10654,15 @@
       <c r="AE14" s="57">
         <v>32.4</v>
       </c>
-      <c r="AF14" s="57"/>
+      <c r="AF14" s="57">
+        <v>35.4</v>
+      </c>
       <c r="AG14" s="57"/>
       <c r="AH14" s="57"/>
       <c r="AI14" s="57"/>
       <c r="AJ14" s="37">
         <f t="shared" si="0"/>
-        <v>32.4</v>
+        <v>35.4</v>
       </c>
       <c r="AK14" s="21">
         <f t="shared" si="1"/>
@@ -10654,11 +10680,11 @@
       </c>
       <c r="AO14" s="23">
         <f t="shared" si="3"/>
-        <v>34.596296296296295</v>
+        <v>34.624999999999993</v>
       </c>
       <c r="AP14" s="23">
         <f t="shared" si="4"/>
-        <v>1.3713596970820632</v>
+        <v>1.4000634007857613</v>
       </c>
     </row>
     <row r="15" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10755,13 +10781,15 @@
       <c r="AE15" s="57">
         <v>32.1</v>
       </c>
-      <c r="AF15" s="57"/>
+      <c r="AF15" s="57">
+        <v>33.299999999999997</v>
+      </c>
       <c r="AG15" s="57"/>
       <c r="AH15" s="57"/>
       <c r="AI15" s="57"/>
       <c r="AJ15" s="37">
         <f t="shared" si="0"/>
-        <v>32.1</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="AK15" s="21">
         <f t="shared" si="1"/>
@@ -10779,11 +10807,11 @@
       </c>
       <c r="AO15" s="23">
         <f t="shared" si="3"/>
-        <v>31.74444444444444</v>
+        <v>31.799999999999994</v>
       </c>
       <c r="AP15" s="23">
         <f t="shared" si="4"/>
-        <v>9.1069883644898653E-3</v>
+        <v>6.4662543920043447E-2</v>
       </c>
     </row>
     <row r="16" spans="1:46" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10929,13 +10957,15 @@
       <c r="AE17" s="57">
         <v>33</v>
       </c>
-      <c r="AF17" s="57"/>
+      <c r="AF17" s="57">
+        <v>35.299999999999997</v>
+      </c>
       <c r="AG17" s="57"/>
       <c r="AH17" s="57"/>
       <c r="AI17" s="57"/>
       <c r="AJ17" s="37">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="AK17" s="21">
         <f t="shared" si="1"/>
@@ -10953,11 +10983,11 @@
       </c>
       <c r="AO17" s="23">
         <f>IF(COUNTIF(E17:AI17,"&gt;0")&gt;=15,AVERAGE(E17:AI17),"")</f>
-        <v>34.077777777777776</v>
+        <v>34.121428571428567</v>
       </c>
       <c r="AP17" s="23">
         <f>IF(AN17&gt;0,IFERROR(AO17-AN17,""),"")</f>
-        <v>1.4037955753306193</v>
+        <v>1.4474463689814101</v>
       </c>
     </row>
     <row r="18" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11054,7 +11084,9 @@
       <c r="AE18" s="57">
         <v>28.5</v>
       </c>
-      <c r="AF18" s="57"/>
+      <c r="AF18" s="57">
+        <v>28.5</v>
+      </c>
       <c r="AG18" s="57"/>
       <c r="AH18" s="57"/>
       <c r="AI18" s="57"/>
@@ -11078,11 +11110,11 @@
       </c>
       <c r="AO18" s="23">
         <f t="shared" ref="AO18:AO33" si="5">IF(COUNTIF(E18:AI18,"&gt;0")&gt;=15,AVERAGE(E18:AI18),"")</f>
-        <v>27.851851851851862</v>
+        <v>27.875000000000007</v>
       </c>
       <c r="AP18" s="23">
         <f t="shared" si="4"/>
-        <v>1.7919809978949921</v>
+        <v>1.8151291460431374</v>
       </c>
     </row>
     <row r="19" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11179,35 +11211,37 @@
       <c r="AE19" s="57">
         <v>35.4</v>
       </c>
-      <c r="AF19" s="57"/>
+      <c r="AF19" s="80">
+        <v>37.6</v>
+      </c>
       <c r="AG19" s="57"/>
       <c r="AH19" s="57"/>
       <c r="AI19" s="57"/>
       <c r="AJ19" s="37">
         <f t="shared" si="0"/>
-        <v>35.4</v>
+        <v>37.6</v>
       </c>
       <c r="AK19" s="21">
         <f t="shared" si="1"/>
-        <v>37.200000000000003</v>
+        <v>37.6</v>
       </c>
       <c r="AL19" s="22">
         <v>37.5</v>
       </c>
       <c r="AM19" s="23">
         <f t="shared" si="2"/>
-        <v>-0.29999999999999716</v>
+        <v>0.10000000000000142</v>
       </c>
       <c r="AN19" s="23">
         <v>33.250962402669643</v>
       </c>
       <c r="AO19" s="23">
         <f t="shared" si="5"/>
-        <v>33.837037037037028</v>
+        <v>33.971428571428568</v>
       </c>
       <c r="AP19" s="23">
         <f t="shared" si="4"/>
-        <v>0.58607463436738527</v>
+        <v>0.72046616875892511</v>
       </c>
     </row>
     <row r="20" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11304,13 +11338,15 @@
       <c r="AE20" s="57">
         <v>30.9</v>
       </c>
-      <c r="AF20" s="57"/>
+      <c r="AF20" s="57">
+        <v>30.7</v>
+      </c>
       <c r="AG20" s="57"/>
       <c r="AH20" s="57"/>
       <c r="AI20" s="57"/>
       <c r="AJ20" s="37">
         <f t="shared" si="0"/>
-        <v>30.9</v>
+        <v>30.7</v>
       </c>
       <c r="AK20" s="21">
         <f t="shared" si="1"/>
@@ -11328,11 +11364,11 @@
       </c>
       <c r="AO20" s="23">
         <f t="shared" si="5"/>
-        <v>30.159259259259262</v>
+        <v>30.178571428571434</v>
       </c>
       <c r="AP20" s="23">
         <f t="shared" si="4"/>
-        <v>1.5184546615581134</v>
+        <v>1.5377668308702859</v>
       </c>
     </row>
     <row r="21" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11429,13 +11465,15 @@
       <c r="AE21" s="57">
         <v>24.1</v>
       </c>
-      <c r="AF21" s="57"/>
+      <c r="AF21" s="57">
+        <v>23.8</v>
+      </c>
       <c r="AG21" s="57"/>
       <c r="AH21" s="57"/>
       <c r="AI21" s="57"/>
       <c r="AJ21" s="37">
         <f t="shared" si="0"/>
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="AK21" s="21">
         <f t="shared" si="1"/>
@@ -11453,11 +11491,11 @@
       </c>
       <c r="AO21" s="23">
         <f t="shared" si="5"/>
-        <v>24.218518518518515</v>
+        <v>24.203571428571422</v>
       </c>
       <c r="AP21" s="23">
         <f t="shared" si="4"/>
-        <v>1.6090153668685439</v>
+        <v>1.5940682769214511</v>
       </c>
     </row>
     <row r="22" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11622,13 +11660,15 @@
       <c r="AE23" s="57">
         <v>27.6</v>
       </c>
-      <c r="AF23" s="57"/>
+      <c r="AF23" s="57">
+        <v>30.2</v>
+      </c>
       <c r="AG23" s="57"/>
       <c r="AH23" s="57"/>
       <c r="AI23" s="57"/>
       <c r="AJ23" s="37">
         <f t="shared" si="0"/>
-        <v>27.6</v>
+        <v>30.2</v>
       </c>
       <c r="AK23" s="21">
         <f t="shared" si="1"/>
@@ -11646,11 +11686,11 @@
       </c>
       <c r="AO23" s="23">
         <f t="shared" si="5"/>
-        <v>28.525925925925929</v>
+        <v>28.585714285714289</v>
       </c>
       <c r="AP23" s="23">
         <f t="shared" si="4"/>
-        <v>1.6575388291517292</v>
+        <v>1.7173271889400894</v>
       </c>
     </row>
     <row r="24" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11747,13 +11787,15 @@
       <c r="AE24" s="57">
         <v>29.1</v>
       </c>
-      <c r="AF24" s="57"/>
+      <c r="AF24" s="57">
+        <v>31.3</v>
+      </c>
       <c r="AG24" s="57"/>
       <c r="AH24" s="57"/>
       <c r="AI24" s="57"/>
       <c r="AJ24" s="37">
         <f t="shared" si="0"/>
-        <v>29.1</v>
+        <v>31.3</v>
       </c>
       <c r="AK24" s="21">
         <f t="shared" si="1"/>
@@ -11771,11 +11813,11 @@
       </c>
       <c r="AO24" s="23">
         <f t="shared" si="5"/>
-        <v>29.43703703703704</v>
+        <v>29.50357142857143</v>
       </c>
       <c r="AP24" s="23">
         <f t="shared" si="4"/>
-        <v>1.1852129202935586</v>
+        <v>1.2517473118279483</v>
       </c>
     </row>
     <row r="25" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11872,13 +11914,15 @@
       <c r="AE25" s="57">
         <v>33.9</v>
       </c>
-      <c r="AF25" s="57"/>
+      <c r="AF25" s="57">
+        <v>34</v>
+      </c>
       <c r="AG25" s="57"/>
       <c r="AH25" s="57"/>
       <c r="AI25" s="57"/>
       <c r="AJ25" s="37">
         <f t="shared" si="0"/>
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="AK25" s="21">
         <f t="shared" si="1"/>
@@ -11896,11 +11940,11 @@
       </c>
       <c r="AO25" s="23">
         <f t="shared" si="5"/>
-        <v>32.451851851851856</v>
+        <v>32.50714285714286</v>
       </c>
       <c r="AP25" s="23">
         <f t="shared" si="4"/>
-        <v>2.075986458630787</v>
+        <v>2.1312774639217906</v>
       </c>
     </row>
     <row r="26" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11997,13 +12041,15 @@
       <c r="AE26" s="57">
         <v>20.2</v>
       </c>
-      <c r="AF26" s="57"/>
+      <c r="AF26" s="57">
+        <v>21.08</v>
+      </c>
       <c r="AG26" s="57"/>
       <c r="AH26" s="57"/>
       <c r="AI26" s="57"/>
       <c r="AJ26" s="37">
         <f t="shared" si="0"/>
-        <v>20.2</v>
+        <v>21.08</v>
       </c>
       <c r="AK26" s="21">
         <f t="shared" si="1"/>
@@ -12021,11 +12067,11 @@
       </c>
       <c r="AO26" s="23">
         <f t="shared" si="5"/>
-        <v>19.681481481481484</v>
+        <v>19.731428571428577</v>
       </c>
       <c r="AP26" s="23">
         <f t="shared" si="4"/>
-        <v>1.1386098740381243</v>
+        <v>1.1885569639852172</v>
       </c>
     </row>
     <row r="27" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12120,13 +12166,15 @@
       <c r="AE27" s="57">
         <v>20</v>
       </c>
-      <c r="AF27" s="57"/>
+      <c r="AF27" s="57">
+        <v>21.2</v>
+      </c>
       <c r="AG27" s="57"/>
       <c r="AH27" s="57"/>
       <c r="AI27" s="57"/>
       <c r="AJ27" s="37">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21.2</v>
       </c>
       <c r="AK27" s="21">
         <f t="shared" si="1"/>
@@ -12144,11 +12192,11 @@
       </c>
       <c r="AO27" s="23">
         <f t="shared" si="5"/>
-        <v>18.946153846153841</v>
+        <v>19.029629629629628</v>
       </c>
       <c r="AP27" s="23">
         <f t="shared" si="4"/>
-        <v>2.2641033020454522</v>
+        <v>2.3475790855212395</v>
       </c>
     </row>
     <row r="28" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12245,13 +12293,15 @@
       <c r="AE28" s="57">
         <v>31.1</v>
       </c>
-      <c r="AF28" s="57"/>
+      <c r="AF28" s="57">
+        <v>32.6</v>
+      </c>
       <c r="AG28" s="57"/>
       <c r="AH28" s="57"/>
       <c r="AI28" s="57"/>
       <c r="AJ28" s="37">
         <f t="shared" si="0"/>
-        <v>31.1</v>
+        <v>32.6</v>
       </c>
       <c r="AK28" s="21">
         <f t="shared" si="1"/>
@@ -12269,11 +12319,11 @@
       </c>
       <c r="AO28" s="23">
         <f t="shared" si="5"/>
-        <v>31.903703703703709</v>
+        <v>31.928571428571434</v>
       </c>
       <c r="AP28" s="23">
         <f t="shared" si="4"/>
-        <v>1.3752511020475495</v>
+        <v>1.4001188269152749</v>
       </c>
     </row>
     <row r="29" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12436,13 +12486,15 @@
       <c r="AE30" s="57">
         <v>37.299999999999997</v>
       </c>
-      <c r="AF30" s="57"/>
+      <c r="AF30" s="57">
+        <v>36.799999999999997</v>
+      </c>
       <c r="AG30" s="57"/>
       <c r="AH30" s="57"/>
       <c r="AI30" s="57"/>
       <c r="AJ30" s="37">
         <f t="shared" si="0"/>
-        <v>37.299999999999997</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="AK30" s="21">
         <f t="shared" si="1"/>
@@ -12460,11 +12512,11 @@
       </c>
       <c r="AO30" s="23">
         <f t="shared" si="5"/>
-        <v>34.900000000000006</v>
+        <v>34.967857142857142</v>
       </c>
       <c r="AP30" s="23">
         <f t="shared" si="4"/>
-        <v>1.1577491039426562</v>
+        <v>1.2256062467997921</v>
       </c>
     </row>
     <row r="31" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12561,13 +12613,15 @@
       <c r="AE31" s="57">
         <v>27</v>
       </c>
-      <c r="AF31" s="57"/>
+      <c r="AF31" s="57">
+        <v>28.3</v>
+      </c>
       <c r="AG31" s="57"/>
       <c r="AH31" s="57"/>
       <c r="AI31" s="57"/>
       <c r="AJ31" s="37">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28.3</v>
       </c>
       <c r="AK31" s="21">
         <f t="shared" si="1"/>
@@ -12585,11 +12639,11 @@
       </c>
       <c r="AO31" s="23">
         <f t="shared" si="5"/>
-        <v>27.24074074074074</v>
+        <v>27.278571428571428</v>
       </c>
       <c r="AP31" s="23">
         <f t="shared" si="4"/>
-        <v>1.8533159036201212</v>
+        <v>1.8911465914508092</v>
       </c>
     </row>
     <row r="32" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12686,13 +12740,15 @@
       <c r="AE32" s="57">
         <v>17.8</v>
       </c>
-      <c r="AF32" s="57"/>
+      <c r="AF32" s="57">
+        <v>18.399999999999999</v>
+      </c>
       <c r="AG32" s="57"/>
       <c r="AH32" s="57"/>
       <c r="AI32" s="57"/>
       <c r="AJ32" s="37">
         <f t="shared" si="0"/>
-        <v>17.8</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="AK32" s="21">
         <f t="shared" si="1"/>
@@ -12710,11 +12766,11 @@
       </c>
       <c r="AO32" s="23">
         <f t="shared" si="5"/>
-        <v>17.770370370370372</v>
+        <v>17.792857142857144</v>
       </c>
       <c r="AP32" s="23">
         <f t="shared" si="4"/>
-        <v>1.4408325971091216</v>
+        <v>1.4633193695958937</v>
       </c>
     </row>
     <row r="33" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12811,13 +12867,15 @@
       <c r="AE33" s="57">
         <v>14.6</v>
       </c>
-      <c r="AF33" s="57"/>
+      <c r="AF33" s="57">
+        <v>15</v>
+      </c>
       <c r="AG33" s="57"/>
       <c r="AH33" s="57"/>
       <c r="AI33" s="57"/>
       <c r="AJ33" s="37">
         <f t="shared" si="0"/>
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="1"/>
@@ -12835,11 +12893,11 @@
       </c>
       <c r="AO33" s="23">
         <f t="shared" si="5"/>
-        <v>15.648148148148149</v>
+        <v>15.625</v>
       </c>
       <c r="AP33" s="23">
         <f t="shared" si="4"/>
-        <v>0.90353561570469942</v>
+        <v>0.88038746755655062</v>
       </c>
       <c r="AT33" s="15"/>
     </row>
@@ -12988,13 +13046,15 @@
       <c r="AE35" s="57">
         <v>33.799999999999997</v>
       </c>
-      <c r="AF35" s="57"/>
+      <c r="AF35" s="57">
+        <v>33.6</v>
+      </c>
       <c r="AG35" s="57"/>
       <c r="AH35" s="57"/>
       <c r="AI35" s="57"/>
       <c r="AJ35" s="37">
         <f t="shared" si="0"/>
-        <v>33.799999999999997</v>
+        <v>33.6</v>
       </c>
       <c r="AK35" s="21">
         <f t="shared" si="1"/>
@@ -13012,11 +13072,11 @@
       </c>
       <c r="AO35" s="23">
         <f>IF(COUNTIF(E35:AI35,"&gt;0")&gt;=15,AVERAGE(E35:AI35),"")</f>
-        <v>31.851851851851848</v>
+        <v>31.914285714285711</v>
       </c>
       <c r="AP35" s="23">
         <f t="shared" si="4"/>
-        <v>0.77915599931728607</v>
+        <v>0.84158986175114947</v>
       </c>
       <c r="AT35" s="15"/>
     </row>
@@ -13234,35 +13294,37 @@
       <c r="AE38" s="57">
         <v>30.6</v>
       </c>
-      <c r="AF38" s="57"/>
+      <c r="AF38" s="57">
+        <v>33.4</v>
+      </c>
       <c r="AG38" s="57"/>
       <c r="AH38" s="57"/>
       <c r="AI38" s="57"/>
       <c r="AJ38" s="37">
         <f t="shared" si="0"/>
-        <v>30.6</v>
+        <v>33.4</v>
       </c>
       <c r="AK38" s="21">
         <f t="shared" si="1"/>
-        <v>33.1</v>
+        <v>33.4</v>
       </c>
       <c r="AL38" s="22">
         <v>38</v>
       </c>
       <c r="AM38" s="23">
         <f t="shared" si="2"/>
-        <v>-4.8999999999999986</v>
+        <v>-4.6000000000000014</v>
       </c>
       <c r="AN38" s="23">
         <v>30.029026223392581</v>
       </c>
       <c r="AO38" s="23">
         <f>IF(COUNTIF(E38:AI38,"&gt;0")&gt;=15,AVERAGE(E38:AI38),"")</f>
-        <v>30.06296296296296</v>
+        <v>30.182142857142853</v>
       </c>
       <c r="AP38" s="23">
         <f t="shared" si="4"/>
-        <v>3.3936739570378904E-2</v>
+        <v>0.15311663375027251</v>
       </c>
       <c r="AT38" s="15"/>
     </row>
@@ -13360,13 +13422,15 @@
       <c r="AE39" s="57">
         <v>33.4</v>
       </c>
-      <c r="AF39" s="57"/>
+      <c r="AF39" s="57">
+        <v>32.4</v>
+      </c>
       <c r="AG39" s="57"/>
       <c r="AH39" s="57"/>
       <c r="AI39" s="57"/>
       <c r="AJ39" s="37">
         <f t="shared" si="0"/>
-        <v>33.4</v>
+        <v>32.4</v>
       </c>
       <c r="AK39" s="21">
         <f t="shared" si="1"/>
@@ -13384,11 +13448,11 @@
       </c>
       <c r="AO39" s="23">
         <f t="shared" ref="AO39:AO48" si="7">IF(COUNTIF(E39:AI39,"&gt;0")&gt;=15,AVERAGE(E39:AI39),"")</f>
-        <v>31.5</v>
+        <v>31.532142857142855</v>
       </c>
       <c r="AP39" s="23">
         <f t="shared" si="4"/>
-        <v>0.65686688913607938</v>
+        <v>0.68900974627893419</v>
       </c>
       <c r="AT39" s="15"/>
     </row>
@@ -13486,13 +13550,15 @@
       <c r="AE40" s="57">
         <v>31.2</v>
       </c>
-      <c r="AF40" s="57"/>
+      <c r="AF40" s="57">
+        <v>32.200000000000003</v>
+      </c>
       <c r="AG40" s="57"/>
       <c r="AH40" s="57"/>
       <c r="AI40" s="57"/>
       <c r="AJ40" s="37">
         <f t="shared" si="0"/>
-        <v>31.2</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="AK40" s="21">
         <f t="shared" si="1"/>
@@ -13510,11 +13576,11 @@
       </c>
       <c r="AO40" s="23">
         <f t="shared" si="7"/>
-        <v>29.966666666666669</v>
+        <v>30.046428571428574</v>
       </c>
       <c r="AP40" s="23">
         <f t="shared" si="4"/>
-        <v>1.0191182795698879</v>
+        <v>1.0988801843317937</v>
       </c>
       <c r="AT40" s="15"/>
     </row>
@@ -13612,13 +13678,15 @@
       <c r="AE41" s="57">
         <v>32.6</v>
       </c>
-      <c r="AF41" s="57"/>
+      <c r="AF41" s="57">
+        <v>33</v>
+      </c>
       <c r="AG41" s="57"/>
       <c r="AH41" s="57"/>
       <c r="AI41" s="57"/>
       <c r="AJ41" s="37">
         <f t="shared" si="0"/>
-        <v>32.6</v>
+        <v>33</v>
       </c>
       <c r="AK41" s="21">
         <f t="shared" si="1"/>
@@ -13636,11 +13704,11 @@
       </c>
       <c r="AO41" s="23">
         <f t="shared" si="7"/>
-        <v>30.629629629629637</v>
+        <v>30.714285714285722</v>
       </c>
       <c r="AP41" s="23">
         <f t="shared" si="4"/>
-        <v>1.2633213859020458</v>
+        <v>1.3479774705581313</v>
       </c>
       <c r="AT41" s="15"/>
     </row>
@@ -13799,13 +13867,15 @@
       <c r="AE43" s="57">
         <v>33.6</v>
       </c>
-      <c r="AF43" s="57"/>
+      <c r="AF43" s="57">
+        <v>32.799999999999997</v>
+      </c>
       <c r="AG43" s="57"/>
       <c r="AH43" s="57"/>
       <c r="AI43" s="57"/>
       <c r="AJ43" s="37">
         <f t="shared" si="0"/>
-        <v>33.6</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="AK43" s="21">
         <f t="shared" si="1"/>
@@ -13823,11 +13893,11 @@
       </c>
       <c r="AO43" s="23">
         <f t="shared" si="7"/>
-        <v>31.275000000000002</v>
+        <v>31.335999999999999</v>
       </c>
       <c r="AP43" s="23">
         <f t="shared" si="4"/>
-        <v>1.2139381720430116</v>
+        <v>1.274938172043008</v>
       </c>
       <c r="AT43" s="15"/>
     </row>
@@ -13923,13 +13993,15 @@
       <c r="AE44" s="57">
         <v>32.299999999999997</v>
       </c>
-      <c r="AF44" s="57"/>
+      <c r="AF44" s="57">
+        <v>31.2</v>
+      </c>
       <c r="AG44" s="57"/>
       <c r="AH44" s="57"/>
       <c r="AI44" s="57"/>
       <c r="AJ44" s="37">
         <f t="shared" si="0"/>
-        <v>32.299999999999997</v>
+        <v>31.2</v>
       </c>
       <c r="AK44" s="21">
         <f t="shared" si="1"/>
@@ -13947,11 +14019,11 @@
       </c>
       <c r="AO44" s="23">
         <f t="shared" si="7"/>
-        <v>31.292307692307688</v>
+        <v>31.288888888888888</v>
       </c>
       <c r="AP44" s="23">
         <f t="shared" si="4"/>
-        <v>2.249120486947227</v>
+        <v>2.2457016835284271</v>
       </c>
       <c r="AT44" s="15"/>
     </row>
@@ -14049,13 +14121,15 @@
       <c r="AE45" s="57">
         <v>32.799999999999997</v>
       </c>
-      <c r="AF45" s="57"/>
+      <c r="AF45" s="57">
+        <v>32</v>
+      </c>
       <c r="AG45" s="57"/>
       <c r="AH45" s="57"/>
       <c r="AI45" s="57"/>
       <c r="AJ45" s="37">
         <f t="shared" si="0"/>
-        <v>32.799999999999997</v>
+        <v>32</v>
       </c>
       <c r="AK45" s="21">
         <f t="shared" si="1"/>
@@ -14073,11 +14147,11 @@
       </c>
       <c r="AO45" s="23">
         <f t="shared" si="7"/>
-        <v>30.688888888888897</v>
+        <v>30.735714285714295</v>
       </c>
       <c r="AP45" s="23">
         <f t="shared" si="4"/>
-        <v>1.1430724960100669</v>
+        <v>1.1898978928354644</v>
       </c>
       <c r="AT45" s="15"/>
     </row>
@@ -14314,13 +14388,15 @@
       <c r="AE48" s="57">
         <v>29.7</v>
       </c>
-      <c r="AF48" s="57"/>
+      <c r="AF48" s="57">
+        <v>32.1</v>
+      </c>
       <c r="AG48" s="57"/>
       <c r="AH48" s="57"/>
       <c r="AI48" s="57"/>
       <c r="AJ48" s="37">
         <f t="shared" si="0"/>
-        <v>29.7</v>
+        <v>32.1</v>
       </c>
       <c r="AK48" s="21">
         <f t="shared" si="1"/>
@@ -14338,11 +14414,11 @@
       </c>
       <c r="AO48" s="23">
         <f t="shared" si="7"/>
-        <v>30.707407407407413</v>
+        <v>30.757142857142863</v>
       </c>
       <c r="AP48" s="23">
         <f t="shared" si="4"/>
-        <v>0.36487455197133301</v>
+        <v>0.41461000170678375</v>
       </c>
     </row>
     <row r="49" spans="5:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -27241,6 +27317,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
@@ -27250,12 +27332,6 @@
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:O13 D15:O31 D33:O34 D36:O46">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">
